--- a/docs/LD_Question_Bank_DRAFT.xlsx
+++ b/docs/LD_Question_Bank_DRAFT.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Read me &amp; coverage" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review (answers &amp; sources)'!$A$1:$K$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review (answers &amp; sources)'!$A$1:$K$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Beyond how many days of Sick Leave is medical proof required?</t>
+          <t>Beyond how many consecutive days of Sick Leave (available to Manager level and above) is medical proof required?</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1919,39 +1919,31 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Within how many days must a travel or expense claim be submitted through Maxvolt One?</t>
+          <t>Overtime applies equally to every department.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15 days</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>90 days</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>7 days</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -1969,31 +1961,47 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Overtime applies equally to every department.</t>
+          <t>Overtime is applicable to which of these departments?</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1;2;3;4;5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
@@ -2011,47 +2019,39 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Overtime is applicable to which of these departments?</t>
+          <t>Flexi hours (for eligible departments/levels) allow an arrival or departure shift of…</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Any time of the employee’s choice</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>±30 minutes, not compensated</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>±2 hours, compensated next week</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
+          <t>±30 minutes, fully compensated the same day</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>1;2;3;4;5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -2074,27 +2074,27 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Flexi hours (for eligible departments/levels) allow an arrival or departure shift of…</t>
+          <t>Your payslip shows a figure you do not understand. Who is the first point of contact?</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>±30 minutes, not compensated</t>
+          <t>Your buddy</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>±2 hours, compensated next week</t>
+          <t>The gate admin</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Any time of the employee’s choice</t>
+          <t>A colleague in another plant</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>±30 minutes, fully compensated the same day</t>
+          <t>Finance / Maxvolt One Helpdesk</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2108,7 +2108,11 @@
       <c r="L33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2124,45 +2128,41 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Your payslip shows a figure you do not understand. Who is the first point of contact?</t>
+          <t>A newer, more detailed approved policy exists for a topic. Which document controls?</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Your buddy</t>
+          <t>The induction presentation</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>The gate admin</t>
+          <t>The current approved policy</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>A colleague in another plant</t>
+          <t>The oldest version</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Finance / Maxvolt One Helpdesk</t>
+          <t>Whatever a colleague remembers</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2173,42 +2173,54 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>A newer, more detailed approved policy exists for a topic. Which document controls?</t>
+          <t>Which of these are zero-tolerance areas under the Code of Conduct?</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>The current approved policy</t>
+          <t>Misuse of company property, data or resources</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>The induction presentation</t>
+          <t>Theft or fraud</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Whatever a colleague remembers</t>
+          <t>Inappropriate language or actions</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The oldest version</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Raising a Helpdesk ticket</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Asking a question about a process</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Harassment</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>1;2;3;6</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="n">
         <v>1</v>
       </c>
@@ -2223,47 +2235,39 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Which of these are zero-tolerance areas under the Code of Conduct?</t>
+          <t>You see inappropriate behaviour at work. What should you do?</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Asking a question about a process</t>
+          <t>Confront the person aggressively</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Inappropriate language or actions</t>
+          <t>Ignore it</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Theft or fraud</t>
+          <t>Report the concern to HR or your supervisor</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Raising a Helpdesk ticket</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Harassment</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Misuse of company property, data or resources</t>
-        </is>
-      </c>
+          <t>Post about it on social media</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2;3;5;6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2274,7 +2278,11 @@
       <c r="L36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2290,34 +2298,34 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>You see inappropriate behaviour at work. What should you do?</t>
+          <t>An employee reports a concern in good faith. What does the Code of Conduct say about retaliation?</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Report the concern to HR or your supervisor</t>
+          <t>It is allowed if the concern turns out to be minor</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Post about it on social media</t>
+          <t>Retaliation is prohibited</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Confront the person aggressively</t>
+          <t>It is only prohibited for senior staff</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Ignore it</t>
+          <t>It is up to the manager</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2328,11 +2336,7 @@
       <c r="L37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2343,39 +2347,31 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>An employee reports a concern in good faith. What does the Code of Conduct say about retaliation?</t>
+          <t>Company data may be used for personal purposes as long as nobody finds out.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Retaliation is prohibited</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>It is up to the manager</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>It is allowed if the concern turns out to be minor</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>It is only prohibited for senior staff</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2397,48 +2393,56 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Company data may be used for personal purposes as long as nobody finds out.</t>
+          <t>A commitment you made is at risk of being delayed. What is the expected behaviour?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Communicate early and keep stakeholders informed</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>Stay silent and hope to catch up</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Blame another department in advance</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Hide the delay until the deadline passes</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2448,27 +2452,27 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>A commitment you made is at risk of being delayed. What is the expected behaviour?</t>
+          <t>You are unsure how to operate a piece of equipment on the floor. What do you do first?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Communicate early and keep stakeholders informed</t>
+          <t>Stop and ask before proceeding</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Stay silent and hope to catch up</t>
+          <t>Try it carefully and see</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Blame another department in advance</t>
+          <t>Carry on and report it later</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Hide the delay until the deadline passes</t>
+          <t>Copy a colleague without asking</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2478,7 +2482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="n">
         <v>1</v>
       </c>
@@ -2502,27 +2510,27 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>You are unsure how to operate a piece of equipment on the floor. What do you do first?</t>
+          <t>Personal protective equipment (PPE) for employees on the floor is…</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Stop and ask before proceeding</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Try it carefully and see</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Carry on and report it later</t>
+          <t>Needed only when a supervisor is watching</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Copy a colleague without asking</t>
+          <t>Needed only for visitors</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2540,11 +2548,7 @@
       <c r="L41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2555,39 +2559,31 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Personal protective equipment (PPE) for employees on the floor is…</t>
+          <t>It is acceptable to bypass a safety control to save time when work is urgent.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Needed only when a supervisor is watching</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Needed only for visitors</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2609,31 +2605,39 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>It is acceptable to bypass a safety control to save time when work is urgent.</t>
+          <t>How should you treat a restricted or controlled area?</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Respect the restriction and enter only when authorised</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>Enter if the door is open</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Enter if a colleague says it is fine</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Enter if you are in a hurry</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2660,34 +2664,34 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>How should you treat a restricted or controlled area?</t>
+          <t>You notice an unsafe situation. What should you do?</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Respect the restriction and enter only when authorised</t>
+          <t>Leave it for the next shift</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Enter if the door is open</t>
+          <t>Fix it yourself without telling anyone</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Enter if you are in a hurry</t>
+          <t>Report it through the appropriate channel</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Enter if a colleague says it is fine</t>
+          <t>Mention it at the next monthly meeting</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2698,7 +2702,11 @@
       <c r="L44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2709,39 +2717,47 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>You notice an unsafe situation. What should you do?</t>
+          <t>Which of these are required safety practices?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Mention it at the next monthly meeting</t>
+          <t>Skip steps when the supervisor is absent</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Fix it yourself without telling anyone</t>
+          <t>Follow applicable safety instructions and SOPs</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Report it through the appropriate channel</t>
+          <t>Use required PPE correctly</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Leave it for the next shift</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+          <t>Respect restricted or controlled areas</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Remove PPE when it is uncomfortable</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Report unsafe situations or incidents</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2;3;4;6</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2752,11 +2768,7 @@
       <c r="L45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2767,47 +2779,31 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Which of these are required safety practices?</t>
+          <t>An incident where nobody was hurt does not need to be reported.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Use required PPE correctly</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Skip steps when the supervisor is absent</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Remove PPE when it is uncomfortable</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Respect restricted or controlled areas</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Report unsafe situations or incidents</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Follow applicable safety instructions and SOPs</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>1;4;5;6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2829,31 +2825,39 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>An incident where nobody was hurt does not need to be reported.</t>
+          <t>A colleague is working on the floor without the required PPE. What should you do?</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Take their photo and post it online</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t>Ignore it — it is their choice</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Wait until someone is hurt</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Speak up and report it through the appropriate channel</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2864,7 +2868,11 @@
       <c r="L47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2880,49 +2888,41 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>A colleague is working on the floor without the required PPE. What should you do?</t>
+          <t>Which Code of Conduct pillar covers environmental requirements and responsible disposal?</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Wait until someone is hurt</t>
+          <t>Respect</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Ignore it — it is their choice</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Take their photo and post it online</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Speak up and report it through the appropriate channel</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2938,34 +2938,34 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Which Code of Conduct pillar covers environmental requirements and responsible disposal?</t>
+          <t>Who is responsible for following safety requirements at Maxvolt?</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Only the safety officer</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Only production employees</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Only new joiners</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Everyone</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
@@ -2988,27 +2988,27 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Who is responsible for following safety requirements at Maxvolt?</t>
+          <t>Maxvolt ReEarth’s circular-economy work reinforces which core value?</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Only new joiners</t>
+          <t>Innovation only</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Only the safety officer</t>
+          <t>Customer Commitment only</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Only production employees</t>
+          <t>None of them</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3033,42 +3033,38 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Maxvolt ReEarth’s circular-economy work reinforces which core value?</t>
+          <t>It is acceptable to ignore a safety instruction when you are sure you know a faster way.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>None of them</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Innovation only</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Customer Commitment only</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L51" s="2" t="n">
         <v>1</v>
       </c>
@@ -3078,31 +3074,39 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>It is acceptable to ignore a safety instruction when you are sure you know a faster way.</t>
+          <t>Maxvolt’s manufacturing facility is certified to which quality-management standard?</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>ISO 27001</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>ISO 9001:2015</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>ISO 45001</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>ISO 14001</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
@@ -3110,11 +3114,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="n">
         <v>1</v>
       </c>
@@ -3134,34 +3134,34 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Maxvolt’s manufacturing facility is certified to which quality-management standard?</t>
+          <t>AIS 156 certification relates to…</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>ISO 14001</t>
+          <t>IT security</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>ISO 45001</t>
+          <t>Payroll compliance</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>ISO 9001:2015</t>
+          <t>Export licences</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>ISO 27001</t>
+          <t>Product safety compliance</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
@@ -3184,34 +3184,34 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AIS 156 certification relates to…</t>
+          <t>Lithium-ion battery packs for two- and three-wheeler electric vehicles belong to which product area?</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Export licences</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Product safety compliance</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Payroll compliance</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>IT security</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -3234,34 +3234,34 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Lithium-ion battery packs for two- and three-wheeler electric vehicles belong to which product area?</t>
+          <t>What does ESS stand for?</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>Emergency Supply Service</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Energy Storage Systems</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>Electric Safety Standard</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>Engineering Support System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
@@ -3284,34 +3284,34 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>What does ESS stand for?</t>
+          <t>Custom battery solutions developed to a partner’s specifications are called…</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Engineering Support System</t>
+          <t>INV solutions</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Electric Safety Standard</t>
+          <t>Retail packs</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Emergency Supply Service</t>
+          <t>OEM solutions</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Energy Storage Systems</t>
+          <t>ESS solutions</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
@@ -3334,34 +3334,34 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Custom battery solutions developed to a partner’s specifications are called…</t>
+          <t>Battery solutions for inverter applications are the…</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>OEM solutions</t>
+          <t>ReEarth area</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Retail packs</t>
+          <t>EV area</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>INV solutions</t>
+          <t>OEM area</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>ESS solutions</t>
+          <t>INV area</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
@@ -3384,34 +3384,34 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Battery solutions for inverter applications are the…</t>
+          <t>In the six-stage operating model, which stage covers diagnostics, claims and replacement support?</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>EV area</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ReEarth area</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>OEM area</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>INV area</t>
+          <t>Distribute</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -3434,34 +3434,34 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>In the six-stage operating model, which stage covers diagnostics, claims and replacement support?</t>
+          <t>Which stage covers reverse logistics, repurposing and recycling?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>Distribute</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Return</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Make</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
@@ -3484,22 +3484,22 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Which stage covers reverse logistics, repurposing and recycling?</t>
+          <t>Testing, validation and certified production belong to which stage?</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Distribute</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Distribute</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
@@ -3534,34 +3534,34 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Testing, validation and certified production belong to which stage?</t>
+          <t>In the requirement-to-customer example, which function handles material control?</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Stores</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Distribute</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
@@ -3584,22 +3584,22 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>In the requirement-to-customer example, which function handles material control?</t>
+          <t>In the same example, which function receives the customer requirement first?</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Purchase</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>Logistics</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Stores</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
@@ -3634,34 +3634,34 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>In the same example, which function receives the customer requirement first?</t>
+          <t>In the circular battery lifecycle, health grading to decide second-life suitability happens at which stage?</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Refine</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Reintegrate</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Assess</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>In the circular battery lifecycle, health grading to decide second-life suitability happens at which stage?</t>
+          <t>At which circular-lifecycle stage are black mass and reusable materials extracted?</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Refine</t>
+          <t>Recover</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
@@ -3734,34 +3734,34 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>At which circular-lifecycle stage are black mass and reusable materials extracted?</t>
+          <t>When does quality begin?</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>Before final testing — Purchase, Stores, Production and others all influence it</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Assess</t>
+          <t>Only after dispatch</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Reintegrate</t>
+          <t>Only at final testing</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Recover</t>
+          <t>Only inside the Quality department</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
@@ -3779,34 +3779,26 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>When does quality begin?</t>
+          <t>Quality is the responsibility of the Quality department alone.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Only at final testing</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Before final testing — Purchase, Stores, Production and others all influence it</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Only after dispatch</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Only inside the Quality department</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
@@ -3829,31 +3821,47 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Quality is the responsibility of the Quality department alone.</t>
+          <t>What should the output you hand to your internal customer be? (choose all that apply)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Clear and traceable</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>Accurate</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Timely</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>As fast as possible even if incomplete</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Understandable only to you</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1;2;3;6</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
@@ -3871,47 +3879,39 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>What should the output you hand to your internal customer be? (choose all that apply)</t>
+          <t>Maxvolt ReEarth is…</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Timely</t>
+          <t>An HR software product</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Understandable only to you</t>
+          <t>The circular-economy subsidiary for battery reuse, recycling and critical-material recovery</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>As fast as possible even if incomplete</t>
+          <t>A solar-panel installer</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Accurate</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Clear and traceable</t>
-        </is>
-      </c>
+          <t>A dealer network</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>1;4;5;6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3934,34 +3934,34 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Maxvolt ReEarth is…</t>
+          <t>What is Maxvolt One?</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>The circular-economy subsidiary for battery reuse, recycling and critical-material recovery</t>
+          <t>A customer-facing shopping site</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>An HR software product</t>
+          <t>A third-party accounting package</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>A dealer network</t>
+          <t>A public social network</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A solar-panel installer</t>
+          <t>The in-house platform for HR, payroll, compliance, recruitment, training and employee services</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
@@ -3984,27 +3984,27 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>What is Maxvolt One?</t>
+          <t>Which e-mail address should you use for company systems?</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>The in-house platform for HR, payroll, compliance, recruitment, training and employee services</t>
+          <t>Your official company e-mail</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>A third-party accounting package</t>
+          <t>A friend’s e-mail</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>A public social network</t>
+          <t>Any personal e-mail</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>A customer-facing shopping site</t>
+          <t>A shared mailbox with no owner</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4034,34 +4034,34 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Which e-mail address should you use for company systems?</t>
+          <t>How is attendance marked where biometric is unavailable?</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Any personal e-mail</t>
+          <t>Selfie + GPS in Maxvolt One</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>A shared mailbox with no owner</t>
+          <t>By e-mailing the manager</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>A friend’s e-mail</t>
+          <t>By phone call to HR</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Your official company e-mail</t>
+          <t>On a paper register only</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -4084,34 +4084,34 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>How is attendance marked where biometric is unavailable?</t>
+          <t>Where can you view and download your payslips?</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>By e-mailing the manager</t>
+          <t>Ask a colleague</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Selfie + GPS in Maxvolt One</t>
+          <t>Company Policies page</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>On a paper register only</t>
+          <t>The gate pass module</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>By phone call to HR</t>
+          <t>My Payslips in Maxvolt One</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -4134,34 +4134,34 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Where can you view and download your payslips?</t>
+          <t>Where do you see your goals, progress and review history?</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>My Payslips in Maxvolt One</t>
+          <t>Gate Pass</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Ask a colleague</t>
+          <t>My Performance</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>The gate pass module</t>
+          <t>Helpdesk</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Company Policies page</t>
+          <t>My Insurance</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
@@ -4184,34 +4184,34 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Where do you see your goals, progress and review history?</t>
+          <t>Where do you request and track premises exit and return?</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Gate Pass</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>Helpdesk</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Gate Pass</t>
-        </is>
-      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>My Insurance</t>
+          <t>My Training</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>My Performance</t>
+          <t>Expenses &amp; Reimbursements</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -4234,34 +4234,34 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Where do you request and track premises exit and return?</t>
+          <t>Where do you see assigned training sessions, your calendar and history?</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Expenses &amp; Reimbursements</t>
+          <t>AskMax</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
+          <t>My Insurance</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>My Performance</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
           <t>My Training</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Gate Pass</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Helpdesk</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
@@ -4284,27 +4284,27 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Where do you see assigned training sessions, your calendar and history?</t>
+          <t>Where do you see your insurance coverage, nominee and claims?</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>My Performance</t>
+          <t>Dashboard only</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>AskMax</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>My Training</t>
+          <t>My Insurance</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>My Insurance</t>
+          <t>My Payslips</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4334,27 +4334,27 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Where do you see your insurance coverage, nominee and claims?</t>
+          <t>Your laptop cannot connect to the office network. Who is your first point of contact?</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Dashboard only</t>
+          <t>Your buddy</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>My Payslips</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>My Insurance</t>
+          <t>IT / Maxvolt One Helpdesk</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>The gate admin</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4368,7 +4368,11 @@
       <c r="L77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
@@ -4384,27 +4388,27 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Your laptop cannot connect to the office network. Who is your first point of contact?</t>
+          <t>You have a policy question late in the evening. What is the quickest way to get an answer?</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>The gate admin</t>
+          <t>Guess</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Your buddy</t>
+          <t>Wait until next month</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>IT / Maxvolt One Helpdesk</t>
+          <t>Ask AskMax, the 24/7 AI assistant</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ask the first colleague you see</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4433,50 +4437,42 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>You have a policy question late in the evening. What is the quickest way to get an answer?</t>
+          <t>Sharing your Maxvolt One password with a colleague to save time is acceptable.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Wait until next month</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Guess</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Ask AskMax, the 24/7 AI assistant</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Ask the first colleague you see</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
@@ -4487,31 +4483,39 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Sharing your Maxvolt One password with a colleague to save time is acceptable.</t>
+          <t>You receive an e-mail from “IT support” asking you to send your Maxvolt One password. What do you do?</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Click the link to check it</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Reply with the password</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Do not share it; report the e-mail to IT through the Helpdesk</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Forward it to friends</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4522,7 +4526,11 @@
       <c r="L80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
@@ -4538,27 +4546,27 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>You receive an e-mail from “IT support” asking you to send your Maxvolt One password. What do you do?</t>
+          <t>You find a colleague’s confidential document on a shared printer. What should you do?</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Click the link to check it</t>
+          <t>Read it for interest</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Reply with the password</t>
+          <t>Leave it for anyone to take</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Do not share it; report the e-mail to IT through the Helpdesk</t>
+          <t>Return it to them or hand it to your supervisor; do not read or copy it</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Forward it to friends</t>
+          <t>Photograph it</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4591,55 +4599,31 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>You find a colleague’s confidential document on a shared printer. What should you do?</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Return it to them or hand it to your supervisor; do not read or copy it</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Photograph it</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Leave it for anyone to take</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Read it for interest</t>
-        </is>
-      </c>
+          <t>Which Maxvolt One module do you use to raise an HR, Finance, IT or Admin ticket?</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>helpdesk;help desk</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4654,7 +4638,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Which Maxvolt One module do you use to raise an HR, Finance, IT or Admin ticket?</t>
+          <t>Name the Maxvolt One module where you apply for leave and see your leave balance.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -4671,43 +4655,59 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>helpdesk;help desk</t>
+          <t>leave</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Name the Maxvolt One module where you apply for leave and see your leave balance.</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>In the “Role Clarity” questions, what does WHY ask?</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Why do other departments exist?</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Who will replace me?</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Why does my work matter?</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Why is my manager busy?</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>leave</t>
-        </is>
-      </c>
+      <c r="N84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4722,34 +4722,34 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>In the “Role Clarity” questions, what does WHY ask?</t>
+          <t>In the “Role Clarity” questions, what does HOW WELL ask?</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Who will replace me?</t>
+          <t>How will my performance be evaluated?</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Why does my work matter?</t>
+          <t>How well is the office decorated?</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Why do other departments exist?</t>
+          <t>How well is the team paid?</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Why is my manager busy?</t>
+          <t>How well do others like me?</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
@@ -4772,27 +4772,27 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>In the “Role Clarity” questions, what does HOW WELL ask?</t>
+          <t>What is the correct order of the role-training model?</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>How well is the team paid?</t>
+          <t>Perform → Learn → Improve → Observe → Practise</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>How will my performance be evaluated?</t>
+          <t>Learn → Observe → Practise → Perform → Improve</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>How well is the office decorated?</t>
+          <t>Practise → Learn → Improve → Perform → Observe</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>How well do others like me?</t>
+          <t>Observe → Perform → Learn → Practise → Improve</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -4822,27 +4822,27 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>What is the correct order of the role-training model?</t>
+          <t>In the “Practise” stage of role training, the employee…</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Perform → Learn → Improve → Observe → Practise</t>
+          <t>Waits for feedback only</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Learn → Observe → Practise → Perform → Improve</t>
+          <t>Performs the task under supervision</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Observe → Perform → Learn → Practise → Improve</t>
+          <t>Completes it fully alone</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Practise → Learn → Improve → Perform → Observe</t>
+          <t>Only watches a demonstration</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -4872,34 +4872,34 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>In the “Practise” stage of role training, the employee…</t>
+          <t>Who is the first point of contact for a department-specific process question?</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Performs the task under supervision</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Waits for feedback only</t>
+          <t>The department SPOC or your Reporting Manager</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Only watches a demonstration</t>
+          <t>The gate admin</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Completes it fully alone</t>
+          <t>Another new joiner</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
@@ -4917,39 +4917,31 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Who is the first point of contact for a department-specific process question?</t>
+          <t>Your buddy replaces your Reporting Manager and formal HR channels.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>The gate admin</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>The department SPOC or your Reporting Manager</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Another new joiner</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -4972,7 +4964,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Your buddy replaces your Reporting Manager and formal HR channels.</t>
+          <t>Formal approvals remain with the authorised roles, not with the buddy.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4991,7 +4983,7 @@
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
@@ -5009,26 +5001,34 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Formal approvals remain with the authorised roles, not with the buddy.</t>
+          <t>What is the theme of Days 61–90?</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Own &amp; Contribute</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>Plan &amp; Prepare</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Learn &amp; Adapt</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Perform &amp; Improve</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
@@ -5056,41 +5056,45 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>What is the theme of Days 61–90?</t>
+          <t>Another department has not given you information you need to finish your work. What is the best response?</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Learn &amp; Adapt</t>
+          <t>Wait silently</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Perform &amp; Improve</t>
+          <t>Guess and proceed</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Plan &amp; Prepare</t>
+          <t>Follow up early and, if still blocked, escalate through the appropriate reporting line</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Own &amp; Contribute</t>
+          <t>Complain about them to others</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
@@ -5106,34 +5110,34 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Another department has not given you information you need to finish your work. What is the best response?</t>
+          <t>You do not know which system or SOP applies to a task in your new role. What should you do?</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Follow up early and, if still blocked, escalate through the appropriate reporting line</t>
+          <t>Use whichever system you used before</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Complain about them to others</t>
+          <t>Skip the task</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Wait silently</t>
+          <t>Ask a friend in another company</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Guess and proceed</t>
+          <t>Ask your Reporting Manager or department SPOC before proceeding</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
@@ -5147,63 +5151,9 @@
       </c>
       <c r="N93" s="2" t="inlineStr"/>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>You do not know which system or SOP applies to a task in your new role. What should you do?</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Skip the task</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Ask your Reporting Manager or department SPOC before proceeding</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Use whichever system you used before</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Ask a friend in another company</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B2:B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"mcq,multi,truefalse,short"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5217,7 +5167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6160,7 +6110,7 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Beyond how many days of Sick Leave is medical proof required?</t>
+          <t>Beyond how many consecutive days of Sick Leave (available to Manager level and above) is medical proof required?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6170,12 +6120,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 12 Leave</t>
+          <t>Training Guide · 12 Leave; Attendance &amp; Leave Policy P002</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>HR policy figure — confirm against the CURRENT approved policy (the guide says the latest approved policy controls). Note the guide gives Sick Leave to Manager &amp; above.</t>
+          <t>HR policy figure — confirm against the CURRENT approved policy (the guide says the latest approved policy controls). Sick Leave is for Manager level and above only — confirmed by HR on 26 Oct 2026.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -6349,23 +6299,23 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Within how many days must a travel or expense claim be submitted through Maxvolt One?</t>
+          <t>Overtime applies equally to every department.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 12 Benefits</t>
+          <t>Training Guide · 12 Working Hours</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -6388,18 +6338,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Overtime applies equally to every department.</t>
+          <t>Overtime is applicable to which of these departments?</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Production; Admin; Store; Logistics; Service</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6427,18 +6377,18 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Overtime is applicable to which of these departments?</t>
+          <t>Flexi hours (for eligible departments/levels) allow an arrival or departure shift of…</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Store; Admin; Service; Logistics; Production</t>
+          <t>±30 minutes, fully compensated the same day</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6472,24 +6422,20 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Flexi hours (for eligible departments/levels) allow an arrival or departure shift of…</t>
+          <t>Your payslip shows a figure you do not understand. Who is the first point of contact?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>±30 minutes, fully compensated the same day</t>
+          <t>Finance / Maxvolt One Helpdesk</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 12 Working Hours</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>HR policy figure — confirm against the CURRENT approved policy (the guide says the latest approved policy controls).</t>
-        </is>
-      </c>
+          <t>Training Guide · 24 Support &amp; Escalation Matrix</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
@@ -6511,17 +6457,17 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Your payslip shows a figure you do not understand. Who is the first point of contact?</t>
+          <t>A newer, more detailed approved policy exists for a topic. Which document controls?</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Finance / Maxvolt One Helpdesk</t>
+          <t>The current approved policy</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 24 Support &amp; Escalation Matrix</t>
+          <t>Training Guide · 12 Policy control</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -6540,23 +6486,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>A newer, more detailed approved policy exists for a topic. Which document controls?</t>
+          <t>Which of these are zero-tolerance areas under the Code of Conduct?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>The current approved policy</t>
+          <t>Misuse of company property, data or resources; Theft or fraud; Inappropriate language or actions; Harassment</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 12 Policy control</t>
+          <t>Training Guide · 11 Zero Tolerance</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -6575,7 +6525,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -6585,17 +6535,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Which of these are zero-tolerance areas under the Code of Conduct?</t>
+          <t>You see inappropriate behaviour at work. What should you do?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Inappropriate language or actions; Theft or fraud; Harassment; Misuse of company property, data or resources</t>
+          <t>Report the concern to HR or your supervisor</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 11 Zero Tolerance</t>
+          <t>Training Guide · 11 Zero Tolerance · 20 Activity 3</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -6624,17 +6574,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>You see inappropriate behaviour at work. What should you do?</t>
+          <t>An employee reports a concern in good faith. What does the Code of Conduct say about retaliation?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Report the concern to HR or your supervisor</t>
+          <t>Retaliation is prohibited</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 11 Zero Tolerance · 20 Activity 3</t>
+          <t>Training Guide · 11 Zero Tolerance</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -6653,7 +6603,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -6663,12 +6613,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>An employee reports a concern in good faith. What does the Code of Conduct say about retaliation?</t>
+          <t>Company data may be used for personal purposes as long as nobody finds out.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Retaliation is prohibited</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -6692,27 +6642,23 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Company data may be used for personal purposes as long as nobody finds out.</t>
+          <t>A commitment you made is at risk of being delayed. What is the expected behaviour?</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Communicate early and keep stakeholders informed</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 11 Zero Tolerance</t>
+          <t>Training Guide · 11 Professional Communication</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -6726,7 +6672,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -6734,20 +6680,24 @@
           <t>mcq</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>A commitment you made is at risk of being delayed. What is the expected behaviour?</t>
+          <t>You are unsure how to operate a piece of equipment on the floor. What do you do first?</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Communicate early and keep stakeholders informed</t>
+          <t>Stop and ask before proceeding</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 11 Professional Communication</t>
+          <t>Training Guide · 9 Safety First</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -6776,17 +6726,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>You are unsure how to operate a piece of equipment on the floor. What do you do first?</t>
+          <t>Personal protective equipment (PPE) for employees on the floor is…</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Stop and ask before proceeding</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 9 Safety First</t>
+          <t>Training Guide · 9 Quality Anchors</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -6805,7 +6755,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -6815,17 +6765,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Personal protective equipment (PPE) for employees on the floor is…</t>
+          <t>It is acceptable to bypass a safety control to save time when work is urgent.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 9 Quality Anchors</t>
+          <t>Training Guide · 9 Safety First</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -6844,7 +6794,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -6854,12 +6804,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>It is acceptable to bypass a safety control to save time when work is urgent.</t>
+          <t>How should you treat a restricted or controlled area?</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Respect the restriction and enter only when authorised</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -6893,12 +6843,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>How should you treat a restricted or controlled area?</t>
+          <t>You notice an unsafe situation. What should you do?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Respect the restriction and enter only when authorised</t>
+          <t>Report it through the appropriate channel</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -6922,7 +6872,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -6932,12 +6882,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>You notice an unsafe situation. What should you do?</t>
+          <t>Which of these are required safety practices?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Report it through the appropriate channel</t>
+          <t>Follow applicable safety instructions and SOPs; Use required PPE correctly; Respect restricted or controlled areas; Report unsafe situations or incidents</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -6961,7 +6911,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -6971,12 +6921,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Which of these are required safety practices?</t>
+          <t>An incident where nobody was hurt does not need to be reported.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Use required PPE correctly; Respect restricted or controlled areas; Report unsafe situations or incidents; Follow applicable safety instructions and SOPs</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -7000,7 +6950,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -7010,12 +6960,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>An incident where nobody was hurt does not need to be reported.</t>
+          <t>A colleague is working on the floor without the required PPE. What should you do?</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Speak up and report it through the appropriate channel</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -7042,24 +6992,20 @@
           <t>mcq</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>A colleague is working on the floor without the required PPE. What should you do?</t>
+          <t>Which Code of Conduct pillar covers environmental requirements and responsible disposal?</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Speak up and report it through the appropriate channel</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 9 Safety First</t>
+          <t>Training Guide · 11 Culture &amp; Code of Conduct</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -7084,17 +7030,17 @@
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Which Code of Conduct pillar covers environmental requirements and responsible disposal?</t>
+          <t>Who is responsible for following safety requirements at Maxvolt?</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Everyone</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 11 Culture &amp; Code of Conduct</t>
+          <t>Training Guide · 4 Core Values · 9 Safety First</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -7119,17 +7065,17 @@
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Who is responsible for following safety requirements at Maxvolt?</t>
+          <t>Maxvolt ReEarth’s circular-economy work reinforces which core value?</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 4 Core Values · 9 Safety First</t>
+          <t>Training Guide · 7 Maxvolt ReEarth</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -7148,23 +7094,27 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>truefalse</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Maxvolt ReEarth’s circular-economy work reinforces which core value?</t>
+          <t>It is acceptable to ignore a safety instruction when you are sure you know a faster way.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Sustainability</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 7 Maxvolt ReEarth</t>
+          <t>Training Guide · 9 Safety First</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -7178,32 +7128,28 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>It is acceptable to ignore a safety instruction when you are sure you know a faster way.</t>
+          <t>Maxvolt’s manufacturing facility is certified to which quality-management standard?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>ISO 9001:2015</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 9 Safety First</t>
+          <t>Training Guide · 9 Quality Anchors</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -7228,12 +7174,12 @@
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Maxvolt’s manufacturing facility is certified to which quality-management standard?</t>
+          <t>AIS 156 certification relates to…</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>ISO 9001:2015</t>
+          <t>Product safety compliance</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -7263,17 +7209,17 @@
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>AIS 156 certification relates to…</t>
+          <t>Lithium-ion battery packs for two- and three-wheeler electric vehicles belong to which product area?</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Product safety compliance</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 9 Quality Anchors</t>
+          <t>Training Guide · 5 Products &amp; Solutions</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -7298,12 +7244,12 @@
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Lithium-ion battery packs for two- and three-wheeler electric vehicles belong to which product area?</t>
+          <t>What does ESS stand for?</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>Energy Storage Systems</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7333,12 +7279,12 @@
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>What does ESS stand for?</t>
+          <t>Custom battery solutions developed to a partner’s specifications are called…</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Energy Storage Systems</t>
+          <t>OEM solutions</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7368,12 +7314,12 @@
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Custom battery solutions developed to a partner’s specifications are called…</t>
+          <t>Battery solutions for inverter applications are the…</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>OEM solutions</t>
+          <t>INV area</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7403,17 +7349,17 @@
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Battery solutions for inverter applications are the…</t>
+          <t>In the six-stage operating model, which stage covers diagnostics, claims and replacement support?</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>INV area</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 5 Products &amp; Solutions</t>
+          <t>Training Guide · 6 Six-Stage Operating Model</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -7438,12 +7384,12 @@
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>In the six-stage operating model, which stage covers diagnostics, claims and replacement support?</t>
+          <t>Which stage covers reverse logistics, repurposing and recycling?</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7473,12 +7419,12 @@
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Which stage covers reverse logistics, repurposing and recycling?</t>
+          <t>Testing, validation and certified production belong to which stage?</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7508,17 +7454,17 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Testing, validation and certified production belong to which stage?</t>
+          <t>In the requirement-to-customer example, which function handles material control?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Stores</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 6 Six-Stage Operating Model</t>
+          <t>Training Guide · 6 Cross-Functional Working</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -7543,12 +7489,12 @@
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>In the requirement-to-customer example, which function handles material control?</t>
+          <t>In the same example, which function receives the customer requirement first?</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Stores</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7578,17 +7524,17 @@
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>In the same example, which function receives the customer requirement first?</t>
+          <t>In the circular battery lifecycle, health grading to decide second-life suitability happens at which stage?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Assess</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 6 Cross-Functional Working</t>
+          <t>Training Guide · 7 Circular Battery Lifecycle</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -7613,12 +7559,12 @@
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>In the circular battery lifecycle, health grading to decide second-life suitability happens at which stage?</t>
+          <t>At which circular-lifecycle stage are black mass and reusable materials extracted?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Assess</t>
+          <t>Recover</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7648,17 +7594,17 @@
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>At which circular-lifecycle stage are black mass and reusable materials extracted?</t>
+          <t>When does quality begin?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Recover</t>
+          <t>Before final testing — Purchase, Stores, Production and others all influence it</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 7 Circular Battery Lifecycle</t>
+          <t>Training Guide · 9 Quality Is Everyone’s Responsibility</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -7677,18 +7623,18 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>When does quality begin?</t>
+          <t>Quality is the responsibility of the Quality department alone.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Before final testing — Purchase, Stores, Production and others all influence it</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7712,23 +7658,23 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Quality is the responsibility of the Quality department alone.</t>
+          <t>What should the output you hand to your internal customer be? (choose all that apply)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Clear and traceable; Accurate; Timely; Complete</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 9 Quality Is Everyone’s Responsibility</t>
+          <t>Training Guide · 10 Internal Customer Principle</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -7747,23 +7693,23 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>What should the output you hand to your internal customer be? (choose all that apply)</t>
+          <t>Maxvolt ReEarth is…</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Timely; Complete; Accurate; Clear and traceable</t>
+          <t>The circular-economy subsidiary for battery reuse, recycling and critical-material recovery</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 10 Internal Customer Principle</t>
+          <t>Training Guide · 7 Maxvolt ReEarth</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -7777,7 +7723,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -7788,17 +7734,17 @@
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Maxvolt ReEarth is…</t>
+          <t>What is Maxvolt One?</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>The circular-economy subsidiary for battery reuse, recycling and critical-material recovery</t>
+          <t>The in-house platform for HR, payroll, compliance, recruitment, training and employee services</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 7 Maxvolt ReEarth</t>
+          <t>Training Guide · 13 Maxvolt One</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -7823,17 +7769,17 @@
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>What is Maxvolt One?</t>
+          <t>Which e-mail address should you use for company systems?</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>The in-house platform for HR, payroll, compliance, recruitment, training and employee services</t>
+          <t>Your official company e-mail</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 13 Maxvolt One</t>
+          <t>Training Guide · 3 New Joiner Preparation</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -7858,17 +7804,17 @@
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Which e-mail address should you use for company systems?</t>
+          <t>How is attendance marked where biometric is unavailable?</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Your official company e-mail</t>
+          <t>Selfie + GPS in Maxvolt One</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 3 New Joiner Preparation</t>
+          <t>Training Guide · 12 · 13 Maxvolt One</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -7893,17 +7839,17 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>How is attendance marked where biometric is unavailable?</t>
+          <t>Where can you view and download your payslips?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Selfie + GPS in Maxvolt One</t>
+          <t>My Payslips in Maxvolt One</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 12 · 13 Maxvolt One</t>
+          <t>Training Guide · 13 Employee Functions</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -7928,12 +7874,12 @@
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Where can you view and download your payslips?</t>
+          <t>Where do you see your goals, progress and review history?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>My Payslips in Maxvolt One</t>
+          <t>My Performance</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -7963,12 +7909,12 @@
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Where do you see your goals, progress and review history?</t>
+          <t>Where do you request and track premises exit and return?</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>My Performance</t>
+          <t>Gate Pass</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -7998,12 +7944,12 @@
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Where do you request and track premises exit and return?</t>
+          <t>Where do you see assigned training sessions, your calendar and history?</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Gate Pass</t>
+          <t>My Training</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8033,12 +7979,12 @@
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Where do you see assigned training sessions, your calendar and history?</t>
+          <t>Where do you see your insurance coverage, nominee and claims?</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>My Training</t>
+          <t>My Insurance</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8068,17 +8014,17 @@
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Where do you see your insurance coverage, nominee and claims?</t>
+          <t>Your laptop cannot connect to the office network. Who is your first point of contact?</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>My Insurance</t>
+          <t>IT / Maxvolt One Helpdesk</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 13 Employee Functions</t>
+          <t>Training Guide · 24 Support &amp; Escalation Matrix</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -8103,17 +8049,17 @@
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Your laptop cannot connect to the office network. Who is your first point of contact?</t>
+          <t>You have a policy question late in the evening. What is the quickest way to get an answer?</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>IT / Maxvolt One Helpdesk</t>
+          <t>Ask AskMax, the 24/7 AI assistant</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 24 Support &amp; Escalation Matrix</t>
+          <t>Training Guide · 13 Employee Functions</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -8132,26 +8078,34 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
+          <t>truefalse</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>You have a policy question late in the evening. What is the quickest way to get an answer?</t>
+          <t>Sharing your Maxvolt One password with a colleague to save time is acceptable.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Ask AskMax, the 24/7 AI assistant</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 13 Employee Functions</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
+          <t>Information-security basics (not in the training guide)</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>NOT in the induction guide — written from general information-security practice. Please have IT / the information-security owner confirm wording.</t>
+        </is>
+      </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
@@ -8167,7 +8121,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -8177,12 +8131,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sharing your Maxvolt One password with a colleague to save time is acceptable.</t>
+          <t>You receive an e-mail from “IT support” asking you to send your Maxvolt One password. What do you do?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Do not share it; report the e-mail to IT through the Helpdesk</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -8192,7 +8146,7 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NOT in the induction guide — written from general information-security practice. Please have IT / the information-security owner confirm wording.</t>
+          <t>NOT in the induction guide — confirm with IT / information-security owner.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -8220,22 +8174,22 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>You receive an e-mail from “IT support” asking you to send your Maxvolt One password. What do you do?</t>
+          <t>You find a colleague’s confidential document on a shared printer. What should you do?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Do not share it; report the e-mail to IT through the Helpdesk</t>
+          <t>Return it to them or hand it to your supervisor; do not read or copy it</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Information-security basics (not in the training guide)</t>
+          <t>Training Guide · 11 Integrity (protect confidential information)</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>NOT in the induction guide — confirm with IT / information-security owner.</t>
+          <t>Confirm wording with the information-security owner.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -8253,34 +8207,26 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>You find a colleague’s confidential document on a shared printer. What should you do?</t>
+          <t>Which Maxvolt One module do you use to raise an HR, Finance, IT or Admin ticket?</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Return it to them or hand it to your supervisor; do not read or copy it</t>
+          <t>any of: helpdesk, help desk</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 11 Integrity (protect confidential information)</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>Confirm wording with the information-security owner.</t>
-        </is>
-      </c>
+          <t>Training Guide · 13 Employee Functions</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
@@ -8302,12 +8248,12 @@
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Which Maxvolt One module do you use to raise an HR, Finance, IT or Admin ticket?</t>
+          <t>Name the Maxvolt One module where you apply for leave and see your leave balance.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>any of: helpdesk, help desk</t>
+          <t>any of: leave</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -8326,28 +8272,28 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Name the Maxvolt One module where you apply for leave and see your leave balance.</t>
+          <t>In the “Role Clarity” questions, what does WHY ask?</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>any of: leave</t>
+          <t>Why does my work matter?</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 13 Employee Functions</t>
+          <t>Training Guide · 15 Role Clarity — Six Questions</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -8372,12 +8318,12 @@
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>In the “Role Clarity” questions, what does WHY ask?</t>
+          <t>In the “Role Clarity” questions, what does HOW WELL ask?</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Why does my work matter?</t>
+          <t>How will my performance be evaluated?</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -8407,17 +8353,17 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>In the “Role Clarity” questions, what does HOW WELL ask?</t>
+          <t>What is the correct order of the role-training model?</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>How will my performance be evaluated?</t>
+          <t>Learn → Observe → Practise → Perform → Improve</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 15 Role Clarity — Six Questions</t>
+          <t>Training Guide · 16 Role Training Methodology</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -8442,12 +8388,12 @@
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>What is the correct order of the role-training model?</t>
+          <t>In the “Practise” stage of role training, the employee…</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Learn → Observe → Practise → Perform → Improve</t>
+          <t>Performs the task under supervision</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -8477,17 +8423,17 @@
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>In the “Practise” stage of role training, the employee…</t>
+          <t>Who is the first point of contact for a department-specific process question?</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Performs the task under supervision</t>
+          <t>The department SPOC or your Reporting Manager</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 16 Role Training Methodology</t>
+          <t>Training Guide · 24 Support &amp; Escalation Matrix</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -8506,23 +8452,23 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>truefalse</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Who is the first point of contact for a department-specific process question?</t>
+          <t>Your buddy replaces your Reporting Manager and formal HR channels.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>The department SPOC or your Reporting Manager</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 24 Support &amp; Escalation Matrix</t>
+          <t>Training Guide · 17 Buddy Boundaries</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -8547,12 +8493,12 @@
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Your buddy replaces your Reporting Manager and formal HR channels.</t>
+          <t>Formal approvals remain with the authorised roles, not with the buddy.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -8576,23 +8522,23 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>truefalse</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Formal approvals remain with the authorised roles, not with the buddy.</t>
+          <t>What is the theme of Days 61–90?</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Own &amp; Contribute</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 17 Buddy Boundaries</t>
+          <t>Training Guide · 19 30/60/90-Day Development Plan</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -8617,17 +8563,17 @@
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>What is the theme of Days 61–90?</t>
+          <t>Another department has not given you information you need to finish your work. What is the best response?</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Own &amp; Contribute</t>
+          <t>Follow up early and, if still blocked, escalate through the appropriate reporting line</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Training Guide · 19 30/60/90-Day Development Plan</t>
+          <t>Training Guide · 20 Activity 3</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -8652,12 +8598,12 @@
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Another department has not given you information you need to finish your work. What is the best response?</t>
+          <t>You do not know which system or SOP applies to a task in your new role. What should you do?</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Follow up early and, if still blocked, escalate through the appropriate reporting line</t>
+          <t>Ask your Reporting Manager or department SPOC before proceeding</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -8670,43 +8616,8 @@
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>You do not know which system or SOP applies to a task in your new role. What should you do?</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Ask your Reporting Manager or department SPOC before proceeding</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Training Guide · 20 Activity 3</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K94"/>
+  <autoFilter ref="A1:K93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8812,7 +8723,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>30</v>
@@ -8822,7 +8733,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4 more needed</t>
+          <t>5 more needed</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8849,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
         <v>140</v>
@@ -9038,7 +8949,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>• The correct option is in a random position for every question (so the answer is not always “first”). The seeded bank has 21 questions, so the bank becomes 114 — enough for a 25-question attempt with different questions on a retake.</t>
+          <t>• The correct option is in a random position for every question (so the answer is not always “first”). The seeded bank has 21 questions, so the bank becomes 113 — enough for a 25-question attempt with different questions on a retake.</t>
         </is>
       </c>
     </row>
